--- a/feedback_surveys/013_event_security_and_safety_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/013_event_security_and_safety_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,8 +880,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -909,12 +909,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'cameras'}</t>
+          <t>cameras</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'cameras'}</t>
+          <t>cameras</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'security_personnel'}</t>
+          <t>security_personnel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'security personnel'}</t>
+          <t>security personnel</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'barriers'}</t>
+          <t>barriers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'barriers'}</t>
+          <t>barriers</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'first_aid_kits'}</t>
+          <t>first_aid_kits</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'first aid kits'}</t>
+          <t>first aid kits</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'emergency_exits'}</t>
+          <t>emergency_exits</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'emergency exits'}</t>
+          <t>emergency exits</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'emergency_contact_information'}</t>
+          <t>emergency_contact_information</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'emergency contact information'}</t>
+          <t>emergency contact information</t>
         </is>
       </c>
     </row>
